--- a/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
+++ b/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,51 @@
           <t>cell_tag</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>run:rest17_after_discovery_guard</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>run:rest17_after_discovery_guard:context_precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>run:rest17_after_discovery_guard:context_recall</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_postfix_20260521</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_postfix_20260521:context_precision</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_postfix_20260521:context_recall</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_cap4_20260521_20260521_200401</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_cap4_20260521_20260521_200401:context_precision</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_cap4_20260521_20260521_200401:context_recall</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -498,6 +543,28 @@
         <is>
           <t>std_hybrid|factual</t>
         </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ISEN 608 §? 0.70, ISEN 608 §? 0.53</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.70, ISEN 608 0.53</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -537,6 +604,39 @@
           <t>std_hybrid|synth|OR|slang</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ISEN 620 §? ?</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ISEN 620 ?, ISEN 620 0.64, ISEN 620 0.58</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ISEN 620 ?, ISEN 620 0.64, ISEN 620 0.58</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -575,6 +675,39 @@
           <t>std_hybrid|synth|EngEcon</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ISEN 667 §? 0.96, ISEN 667 §? 0.94, ISEN 667 §? 0.96, ISEN 667 §? 0.78, ISEN 660 §? 0.82, ISEN 660 §? 0.82</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.96, ISEN 667 0.94, ISEN 660 0.82, ISEN 660 0.82</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.96, ISEN 667 0.94, ISEN 667 0.96, ISEN 667 0.78, ISEN 660 0.82, ISEN 660 0.82</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6667</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -613,6 +746,28 @@
           <t>std_hybrid|structural|ESL</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ISEN 667 §? 0.75, ISEN 667 §? 0.70, ISEN 667 §? 0.69</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.75, ISEN 667 0.70</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -651,6 +806,39 @@
           <t>std_hybrid|prereq</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ISEN 665 §? 0.73</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.73</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.73</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -689,6 +877,28 @@
           <t>std_hybrid|grading|SysEng</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ISEN 640 §? 0.82, ISEN 640 §? 0.81</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.82, ISEN 640 0.81</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -727,6 +937,28 @@
           <t>std_hybrid|grading|verbose</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ISEN 614 §? 0.83</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.83</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -765,6 +997,39 @@
           <t>std_semantic|discovery|HF+PM</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ISEN 635 §? 0.78, ISEN 635 §? 0.71, ISEN 635 §? 0.88, ISEN 608 §? 0.94, ISEN 665 §? 0.84, ISEN 634 §? 0.81, ISEN 634 §? 0.79</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 608 0.94, ISEN 665 0.84, ISEN 634 0.81, ISEN 634 0.79</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 635 0.88, ISEN 608 0.94, ISEN 665 0.84, ISEN 634 0.81, ISEN 634 0.79</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -803,6 +1068,28 @@
           <t>std_semantic|discovery|SysEng|ESL</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ISEN 641 §? 0.93, ISEN 641 §? 0.88, ISEN 641 §? 0.84, ISEN 641 §? 0.80, ISEN 640 §? 0.79, ISEN 640 §? 0.79, ISEN 640 §? 0.78</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.93, ISEN 641 0.88, ISEN 641 0.84, ISEN 641 0.80, ISEN 640 0.79, ISEN 640 0.78</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -841,6 +1128,28 @@
           <t>std_semantic|compare|DOE|verbose</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ISEN 616 §? 0.89, ISEN 613 §? 0.74, ISEN 616 §? 0.80, ISEN 616 §? 0.76, ISEN 613 §? 0.70, ISEN 613 §? 0.75, ISEN 627 §? 0.72, ISEN 613 §? 0.72, ISEN 614 §? 0.70, ISEN 614 §? 0.69, ISEN 613 §? 0.68</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.89, ISEN 613 0.74, ISEN 616 0.80, ISEN 616 0.76, ISEN 613 0.70, ISEN 627 0.72, ISEN 614 0.70, ISEN 614 0.69, ISEN 613 0.68</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -879,6 +1188,39 @@
           <t>std_semantic|discovery|6sigma</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ISEN 645 §? 0.80, ISEN 645 §? 0.61, ISEN 645 §? 0.77, ISEN 645 §? 0.70, ISEN 645 §? 0.62</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.80, ISEN 645 0.61</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.80, ISEN 645 0.61, ISEN 645 0.70, ISEN 645 0.62</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -917,6 +1259,39 @@
           <t>std_semantic|discovery|OR|ESL</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ISEN 622 §? 0.72, ISEN 622 §? 0.72, ISEN 622 §? 0.70, ISEN 622 §? 0.70, ISEN 620 §? 0.70, ISEN 620 §? 0.70, ISEN 620 §? 0.70, ISEN 620 §? 0.70, ISEN 620 §? 0.70, ISEN 620 §? 0.69, ISEN 620 §? 0.68, ISEN 620 §? 0.66, ISEN 620 §? 0.66, ISEN 620 §? 0.66, ISEN 620 §? 0.66, ISEN 620 §? 0.66, ISEN 620 §? 0.62, ISEN 620 §? 0.62, ISEN 689 §? 0.61, ISEN 689 §? 0.59</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 689 0.61, ISEN 689 0.59</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 689 0.61, ISEN 689 0.59</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -955,6 +1330,28 @@
           <t>std_semantic|discovery|Lean</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ISEN 645 §? 0.66, ISEN 645 §? 0.66, ISEN 658 §? 0.77, ISEN 645 §? 0.68, ISEN 645 §? 0.62</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.66, ISEN 645 0.66, ISEN 658 0.77, ISEN 645 0.68</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -993,6 +1390,28 @@
           <t>std_semantic|temporal_align|HW2</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ISEN 617 §? 0.66, ISEN 615 §? 0.59, ISEN 665 §? 0.64, ISEN 615 §? 0.62, ISEN 615 §? 0.62</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.66, ISEN 615 0.59, ISEN 665 0.64, ISEN 615 0.62, ISEN 615 0.62</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1036,6 +1455,39 @@
           <t>adv|conjunctive|Wiley+PM</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ISEN 608 §? 0.59, ISEN 665 §? 0.52, ISEN 608 §? 0.54</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52, ISEN 608 0.54</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52, ISEN 608 0.54</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1079,6 +1531,28 @@
           <t>adv|out_of_scope</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ISEN 645 §? 0.64, ISEN 645 §? 0.52, ISEN 645 §? 0.41</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.64, ISEN 645 0.52, ISEN 645 0.41</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1122,6 +1596,39 @@
           <t>adv|buried_detail|author</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ISEN 630 §? 0.90, ISEN 630 §? 0.90</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.90, ISEN 630 0.90</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.90, ISEN 630 0.90</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1165,6 +1672,39 @@
           <t>adv|multi_crn|sim</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ISEN 625 §? 0.66, ISEN 625 §? 0.67, ISEN 625 §? 0.62, ISEN 625 §? 0.82, ISEN 625 §? 0.72, ISEN 641 §? 0.64, ISEN 625 §? 0.83</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.66, ISEN 625 0.67, ISEN 641 0.64</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.66, ISEN 625 0.67, ISEN 625 0.62, ISEN 625 0.72, ISEN 641 0.64</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1208,6 +1748,39 @@
           <t>adv|multi_crn|lean</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ISEN 645 §? 0.88, ISEN 645 §? 0.80, ISEN 645 §? 0.89, ISEN 645 §? 0.85, ISEN 645 §? 0.79, ISEN 645 §? 0.80, ISEN 645 §? 0.76, ISEN 615 §? 0.68, ISEN 658 §? 0.79, ISEN 658 §? 0.75, ISEN 689 §? 0.70, ISEN 615 §? 0.68, ISEN 645 §? 0.73</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.80, ISEN 615 0.68, ISEN 658 0.79, ISEN 658 0.75, ISEN 689 0.70, ISEN 615 0.68</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.80, ISEN 645 0.85, ISEN 645 0.79, ISEN 615 0.68, ISEN 658 0.79, ISEN 658 0.75, ISEN 689 0.70, ISEN 615 0.68</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1250,6 +1823,39 @@
         <is>
           <t>adv|numeric_trap|exam2_30pct</t>
         </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ISEN 689 §? 0.68, ISEN 633 §? 0.74, ISEN 625 §? 0.70, ISEN 625 §? 0.67, ISEN 660 §? 0.80, ISEN 658 §? 0.70, ISEN 660 §? 0.77, ISEN 660 §? 0.70, ISEN 615 §? 0.74, ISEN 660 §? 0.70, ISEN 620 §? 0.71, ISEN 640 §? 0.69, ISEN 658 §? 0.70, ISEN 640 §? 0.68, ISEN 616 §? 0.68</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.68, ISEN 633 0.74, ISEN 625 0.70, ISEN 625 0.67, ISEN 660 0.80, ISEN 658 0.70, ISEN 660 0.77, ISEN 615 0.74, ISEN 620 0.71, ISEN 640 0.69, ISEN 658 0.70, ISEN 616 0.68</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.68, ISEN 633 0.74, ISEN 625 0.70, ISEN 625 0.67, ISEN 660 0.80, ISEN 658 0.70, ISEN 660 0.77, ISEN 660 0.70, ISEN 615 0.74, ISEN 660 0.70, ISEN 620 0.71, ISEN 640 0.69, ISEN 658 0.70, ISEN 616 0.68</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
+++ b/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,21 @@
           <t>run:curated20_v2_cap4_20260521_20260521_200401:context_recall</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_q2_use_summary_guard_20260521</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_q2_use_summary_guard_20260521:context_precision</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>run:curated20_v2_q2_use_summary_guard_20260521:context_recall</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -636,6 +651,17 @@
       </c>
       <c r="R3" t="n">
         <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.65, ISEN 620 0.58, ISEN 620 0.57, ISEN 620 0.64, ISEN 620 0.65</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">

--- a/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
+++ b/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,36 @@
           <t>run:curated20_v2_q2_use_summary_guard_20260521:context_recall</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>run:primer_off_803b790_20260522_032432</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>run:primer_off_803b790_20260522_032432:context_precision</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>run:primer_off_803b790_20260522_032432:context_recall</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>run:primer_on_803b790_20260522_033654</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>run:primer_on_803b790_20260522_033654:context_precision</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>run:primer_on_803b790_20260522_033654:context_recall</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -579,6 +609,28 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.70, ISEN 608 0.53</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.70, ISEN 608 0.53</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -663,6 +715,28 @@
       <c r="U3" t="n">
         <v>1</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.65, ISEN 620 0.58, ISEN 620 0.57, ISEN 620 0.64, ISEN 620 0.65</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.65, ISEN 620 0.58, ISEN 620 0.57, ISEN 620 0.64, ISEN 620 0.65</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -734,6 +808,28 @@
       <c r="R4" t="n">
         <v>0.6667</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.96, ISEN 667 0.94, ISEN 667 0.96, ISEN 667 0.78, ISEN 660 0.82, ISEN 660 0.82</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.96, ISEN 667 0.94, ISEN 667 0.96, ISEN 667 0.78, ISEN 660 0.82, ISEN 660 0.82</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6667</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -794,6 +890,28 @@
       <c r="R5" t="n">
         <v>1</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.75, ISEN 667 0.70</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.75, ISEN 667 0.70</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -865,6 +983,28 @@
       <c r="R6" t="n">
         <v>1</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.73</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.73</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -925,6 +1065,28 @@
       <c r="R7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.82, ISEN 640 0.81</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.82, ISEN 640 0.81</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -985,6 +1147,28 @@
       <c r="R8" t="n">
         <v>1</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.83</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.83</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1056,6 +1240,28 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 635 0.88, ISEN 608 0.94, ISEN 665 0.84, ISEN 634 0.81, ISEN 634 0.79</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 635 0.88, ISEN 608 0.94, ISEN 665 0.84, ISEN 634 0.81, ISEN 634 0.79</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1116,6 +1322,28 @@
       <c r="R10" t="n">
         <v>1</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.93, ISEN 641 0.88, ISEN 641 0.84, ISEN 641 0.80, ISEN 640 0.79, ISEN 640 0.78</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.93, ISEN 641 0.88, ISEN 641 0.84, ISEN 641 0.80, ISEN 640 0.79, ISEN 640 0.78</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1176,6 +1404,28 @@
       <c r="R11" t="n">
         <v>1</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.89, ISEN 613 0.74, ISEN 616 0.80, ISEN 616 0.76, ISEN 613 0.70, ISEN 627 0.72, ISEN 614 0.70, ISEN 614 0.69, ISEN 613 0.68</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.89, ISEN 613 0.74, ISEN 616 0.80, ISEN 616 0.76, ISEN 613 0.70, ISEN 627 0.72, ISEN 614 0.70, ISEN 614 0.69, ISEN 613 0.68</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1247,6 +1497,28 @@
       <c r="R12" t="n">
         <v>1</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.80, ISEN 645 0.61, ISEN 645 0.70, ISEN 645 0.62</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.80, ISEN 645 0.61, ISEN 645 0.70, ISEN 645 0.62</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1318,6 +1590,28 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 689 0.61, ISEN 689 0.59</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 689 0.61, ISEN 689 0.59</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1378,6 +1672,28 @@
       <c r="R14" t="n">
         <v>0.5</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.66, ISEN 645 0.66, ISEN 658 0.77, ISEN 645 0.68</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.66, ISEN 645 0.66, ISEN 658 0.77, ISEN 645 0.68</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1438,6 +1754,28 @@
       <c r="R15" t="n">
         <v>1</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.66, ISEN 615 0.59, ISEN 665 0.64, ISEN 615 0.62, ISEN 615 0.62</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.66, ISEN 615 0.59, ISEN 665 0.64, ISEN 615 0.62, ISEN 615 0.62</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1514,6 +1852,28 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52, ISEN 608 0.54</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52, ISEN 608 0.54</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1579,6 +1939,28 @@
       <c r="R17" t="n">
         <v>1</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.64, ISEN 645 0.52, ISEN 645 0.41</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.64, ISEN 645 0.52, ISEN 645 0.41</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1655,6 +2037,28 @@
       <c r="R18" t="n">
         <v>1</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.90, ISEN 630 0.90</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.90, ISEN 630 0.90</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1731,6 +2135,28 @@
       <c r="R19" t="n">
         <v>0.2</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.66, ISEN 625 0.67, ISEN 625 0.62, ISEN 625 0.72, ISEN 641 0.64</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.66, ISEN 625 0.67, ISEN 625 0.62, ISEN 625 0.72, ISEN 641 0.64</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1807,6 +2233,28 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.80, ISEN 645 0.85, ISEN 645 0.79, ISEN 615 0.68, ISEN 658 0.79, ISEN 658 0.75, ISEN 689 0.70, ISEN 615 0.68</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.80, ISEN 645 0.85, ISEN 645 0.79, ISEN 615 0.68, ISEN 658 0.79, ISEN 658 0.75, ISEN 689 0.70, ISEN 615 0.68</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1881,6 +2329,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.68, ISEN 633 0.74, ISEN 625 0.70, ISEN 625 0.67, ISEN 660 0.80, ISEN 658 0.70, ISEN 660 0.77, ISEN 660 0.70, ISEN 615 0.74, ISEN 660 0.70, ISEN 620 0.71, ISEN 640 0.69, ISEN 658 0.70, ISEN 616 0.68</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.68, ISEN 633 0.74, ISEN 625 0.70, ISEN 625 0.67, ISEN 660 0.80, ISEN 658 0.70, ISEN 660 0.77, ISEN 660 0.70, ISEN 615 0.74, ISEN 660 0.70, ISEN 620 0.71, ISEN 640 0.69, ISEN 658 0.70, ISEN 616 0.68</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
+++ b/tamu_data/evals/golden_sets/ragas_20260519_curated20_v2.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,51 @@
           <t>run:primer_on_803b790_20260522_033654:context_recall</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_20260522_195334</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_20260522_195334:context_precision</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_20260522_195334:context_recall</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_v2_20260522_201712</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_v2_20260522_201712:context_precision</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>run:router_flashlite_20260522_v2_20260522_201712:context_recall</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>run:chunk_600t_100o_fixed_20260522</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>run:chunk_600t_100o_fixed_20260522:context_precision</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>run:chunk_600t_100o_fixed_20260522:context_recall</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -631,6 +676,39 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.70, ISEN 608 0.53</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.80, ISEN 608 0.75, ISEN 608 0.41, ISEN 608 0.56</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.88, ISEN 608 0.32</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -737,6 +815,39 @@
       <c r="AA3" t="n">
         <v>1</v>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.65, ISEN 620 0.58, ISEN 620 0.57, ISEN 620 0.64, ISEN 620 0.65</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>ISEN 620 ?, ISEN 620 0.71, ISEN 620 0.48</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.85</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -830,6 +941,39 @@
       <c r="AA4" t="n">
         <v>0.6667</v>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.96, ISEN 667 0.94, ISEN 667 0.96, ISEN 667 0.78, ISEN 660 0.82, ISEN 660 0.82</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.93, ISEN 667 0.89, ISEN 667 0.92, ISEN 667 0.81, ISEN 660 0.68, ISEN 660 0.68</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.90, ISEN 667 0.89, ISEN 667 0.92</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.6667</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -912,6 +1056,39 @@
       <c r="AA5" t="n">
         <v>1</v>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.75, ISEN 667 0.70</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.64, ISEN 667 0.78, ISEN 667 0.53, ISEN 667 0.59</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>ISEN 667 0.89, ISEN 667 0.66</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1005,6 +1182,39 @@
       <c r="AA6" t="n">
         <v>1</v>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.73</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.86</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>ISEN 665 0.80, ISEN 665 0.78, ISEN 665 0.66, ISEN 665 0.65</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1087,6 +1297,39 @@
       <c r="AA7" t="n">
         <v>1</v>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.82, ISEN 640 0.81</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.70</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>ISEN 640 0.88</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1169,6 +1412,39 @@
       <c r="AA8" t="n">
         <v>1</v>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.83</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.89</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>ISEN 614 0.90, ISEN 614 0.79</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1262,6 +1538,39 @@
       <c r="AA9" t="n">
         <v>0</v>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 635 0.88, ISEN 608 0.94, ISEN 665 0.84, ISEN 634 0.81, ISEN 634 0.79</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.78, ISEN 635 0.71, ISEN 635 0.87, ISEN 608 0.94, ISEN 665 0.82, ISEN 634 0.80, ISEN 634 0.77, ISEN 635 0.73</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>ISEN 635 0.82, ISEN 635 0.78, ISEN 608 0.94, ISEN 608 0.89, ISEN 634 0.80, ISEN 634 0.80, ISEN 635 0.79, ISEN 635 0.73</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1344,6 +1653,39 @@
       <c r="AA10" t="n">
         <v>1</v>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.93, ISEN 641 0.88, ISEN 641 0.84, ISEN 641 0.80, ISEN 640 0.79, ISEN 640 0.78</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.93, ISEN 641 0.87</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>ISEN 641 0.94, ISEN 641 0.87, ISEN 641 0.83, ISEN 641 0.79</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1426,6 +1768,39 @@
       <c r="AA11" t="n">
         <v>1</v>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.89, ISEN 613 0.74, ISEN 616 0.80, ISEN 616 0.76, ISEN 613 0.70, ISEN 627 0.72, ISEN 614 0.70, ISEN 614 0.69, ISEN 613 0.68</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.90</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>ISEN 616 0.95</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1519,6 +1894,39 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.80, ISEN 645 0.61, ISEN 645 0.70, ISEN 645 0.62</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.6389</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.82</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.82, ISEN 645 0.82, ISEN 645 0.80</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1612,6 +2020,39 @@
       <c r="AA13" t="n">
         <v>0</v>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 620 0.70, ISEN 689 0.61, ISEN 689 0.59</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>ISEN 622 0.70, ISEN 620 0.67, ISEN 620 0.66, ISEN 622 0.66, ISEN 620 0.65, ISEN 620 0.65</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>ISEN 620 0.73, ISEN 620 0.72, ISEN 622 0.72, ISEN 622 0.70, ISEN 620 0.70, ISEN 620 0.70</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1694,6 +2135,39 @@
       <c r="AA14" t="n">
         <v>0.5</v>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.66, ISEN 645 0.66, ISEN 658 0.77, ISEN 645 0.68</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>ISEN 658 0.71, ISEN 645 0.65, ISEN 645 0.64, ISEN 645 0.61, ISEN 658 0.57, ISEN 689 0.52, ISEN 645 0.50</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>ISEN 658 0.70, ISEN 645 0.69, ISEN 645 0.66, ISEN 645 0.65, ISEN 645 0.63, ISEN 658 0.56, ISEN 689 0.52, ISEN 641 0.41</t>
+        </is>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1776,6 +2250,39 @@
       <c r="AA15" t="n">
         <v>0</v>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.66, ISEN 615 0.59, ISEN 665 0.64, ISEN 615 0.62, ISEN 615 0.62</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.61, ISEN 615 0.71, ISEN 615 0.58, ISEN 665 0.57, ISEN 615 0.58</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>ISEN 617 0.71, ISEN 617 0.67, ISEN 615 0.71, ISEN 617 0.62, ISEN 665 0.70, ISEN 665 0.70, ISEN 615 0.65</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1874,6 +2381,39 @@
       <c r="AA16" t="n">
         <v>0</v>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52, ISEN 608 0.54</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.59, ISEN 665 0.52</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>ISEN 608 0.73, ISEN 608 0.59</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1961,6 +2501,39 @@
       <c r="AA17" t="n">
         <v>1</v>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.64, ISEN 645 0.52, ISEN 645 0.41</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.65, ISEN 645 0.52, ISEN 645 0.75, ISEN 645 0.53, ISEN 645 0.51</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.64</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2059,6 +2632,39 @@
       <c r="AA18" t="n">
         <v>1</v>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.90, ISEN 630 0.90</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.91, ISEN 630 0.91</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>ISEN 630 0.95, ISEN 630 0.95, ISEN 630 0.88, ISEN 630 0.83</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2157,6 +2763,39 @@
       <c r="AA19" t="n">
         <v>0.2</v>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.66, ISEN 625 0.67, ISEN 625 0.62, ISEN 625 0.72, ISEN 641 0.64</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.73, ISEN 625 0.73, ISEN 625 0.67, ISEN 625 0.68</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>ISEN 625 0.80, ISEN 625 0.76, ISEN 625 0.72</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2255,6 +2894,39 @@
       <c r="AA20" t="n">
         <v>0</v>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.88, ISEN 645 0.80, ISEN 645 0.85, ISEN 645 0.79, ISEN 615 0.68, ISEN 658 0.79, ISEN 658 0.75, ISEN 689 0.70, ISEN 615 0.68</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.87, ISEN 645 0.87, ISEN 645 0.84, ISEN 645 0.76</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>ISEN 645 0.89, ISEN 645 0.84, ISEN 645 0.84, ISEN 658 0.80, ISEN 645 0.80</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2352,6 +3024,39 @@
       </c>
       <c r="AA21" t="n">
         <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.68, ISEN 633 0.74, ISEN 625 0.70, ISEN 625 0.67, ISEN 660 0.80, ISEN 658 0.70, ISEN 660 0.77, ISEN 660 0.70, ISEN 615 0.74, ISEN 660 0.70, ISEN 620 0.71, ISEN 640 0.69, ISEN 658 0.70, ISEN 616 0.68</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>ISEN 633 0.80, ISEN 689 0.76</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>ISEN 689 0.79, ISEN 689 0.79, ISEN 633 0.79, ISEN 689 0.78</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
